--- a/data/fsa/2026_ERP.xlsx
+++ b/data/fsa/2026_ERP.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\EPAS\2014FBIMP\ARC_PLC\Webpage Posting\2026-0911\Program Year 2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\EPAS\2014FBIMP\ARC_PLC\Webpage Posting\2026-1009\Program Year 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{426EBC71-8D11-42CE-8F6B-0950C0537200}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B86F891B-D04A-4FB0-89A5-58B615DBD2A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
     <t>BASED ON 2020/21-2024/25 MARKET YEAR AVERAGE (MYA) PRICES AND REFERENCE PRICES</t>
   </si>
   <si>
-    <t>September 11, 2026 1/</t>
+    <t>October 9, 2026 1/</t>
   </si>
   <si>
     <t>Commodity</t>
@@ -1751,6 +1751,6 @@
     <mergeCell ref="A33:L33"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="1.6" header="0" footer="0"/>
-  <pageSetup scale="86" orientation="landscape" cellComments="atEnd" horizontalDpi="2400" verticalDpi="2400" r:id="rId1"/>
+  <pageSetup scale="87" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>